--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D133"/>
+  <dimension ref="A1:D138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2419,20 +2419,14 @@
           <t>vJqPCEPP</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="B125" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C125" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D125" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="126">
@@ -2441,20 +2435,14 @@
           <t>2Hl43AnC</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B126" t="n">
+        <v>2</v>
+      </c>
+      <c r="C126" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D126" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="127">
@@ -2463,20 +2451,14 @@
           <t>SIOxI915</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="B127" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C127" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D127" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="128">
@@ -2485,20 +2467,14 @@
           <t>EeIMLi2t</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="B128" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C128" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D128" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="129">
@@ -2507,20 +2483,14 @@
           <t>fiod5WHa</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
+      <c r="B129" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C129" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D129" t="n">
+        <v>5.75</v>
       </c>
     </row>
     <row r="130">
@@ -2529,20 +2499,14 @@
           <t>OWxD1lHO</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B130" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C130" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D130" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="131">
@@ -2551,20 +2515,14 @@
           <t>zkVf7hmm</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B131" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C131" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D131" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="132">
@@ -2573,20 +2531,14 @@
           <t>f5QUJVWh</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B132" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C132" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D132" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="133">
@@ -2595,19 +2547,123 @@
           <t>OA1xkBXI</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
+      <c r="B133" t="n">
+        <v>2</v>
+      </c>
+      <c r="C133" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D133" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>IViLLjPF</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
         <is>
           <t>3.60</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>tC1Aa08D</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>YJ3eN30K</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>h4pSHsOs</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
         <is>
           <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>StuiCwhJ</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2.80</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D138"/>
+  <dimension ref="A1:D169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2563,20 +2563,14 @@
           <t>IViLLjPF</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
+      <c r="B134" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C134" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D134" t="n">
+        <v>3.75</v>
       </c>
     </row>
     <row r="135">
@@ -2585,20 +2579,14 @@
           <t>tC1Aa08D</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
+      <c r="B135" t="n">
+        <v>4</v>
+      </c>
+      <c r="C135" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.83</v>
       </c>
     </row>
     <row r="136">
@@ -2607,20 +2595,14 @@
           <t>YJ3eN30K</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="B136" t="n">
+        <v>3</v>
+      </c>
+      <c r="C136" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="137">
@@ -2629,20 +2611,14 @@
           <t>h4pSHsOs</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B137" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C137" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="138">
@@ -2651,19 +2627,695 @@
           <t>StuiCwhJ</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
+      <c r="B138" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C138" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D138" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>QHrzGLhf</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>KdD11Mw1</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>MqxqEaN6</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>CW9g3r9l</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>pzHxyrtm</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>dCPKovw8</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>vXAKoaf5</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>YV3TqwPH</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>l0ueP5rR</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>t2AoZLAa</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>23.00</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>jFMCm08e</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>tvOIPExA</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>KSwfVwAO</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>6q2yrHgU</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>AiJ3kset</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>hzyf0b9b</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>CpiTEcOi</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>8CpxDyg4</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>41.00</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>bF2q76Mr</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>vyk5gjdE</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>tbKZHNz1</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
         <is>
           <t>3.30</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2.80</t>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>MZjh9ghT</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>f1nnRRDE</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>8QPARz8c</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>0K2qBFNG</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>Kj4sifWp</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>34.00</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>lONsG15D</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>pWQQJq6l</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>hIsO3XFj</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>EF8gXauC</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>fcxqFy2l</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>4.33</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D138"/>
+  <dimension ref="A1:D173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2563,20 +2563,14 @@
           <t>IViLLjPF</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
+      <c r="B134" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C134" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D134" t="n">
+        <v>3.75</v>
       </c>
     </row>
     <row r="135">
@@ -2585,20 +2579,14 @@
           <t>tC1Aa08D</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
+      <c r="B135" t="n">
+        <v>4</v>
+      </c>
+      <c r="C135" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.83</v>
       </c>
     </row>
     <row r="136">
@@ -2607,20 +2595,14 @@
           <t>YJ3eN30K</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="B136" t="n">
+        <v>3</v>
+      </c>
+      <c r="C136" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="137">
@@ -2629,20 +2611,14 @@
           <t>h4pSHsOs</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B137" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C137" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="138">
@@ -2651,19 +2627,597 @@
           <t>StuiCwhJ</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2.80</t>
+      <c r="B138" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C138" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D138" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>QHrzGLhf</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C139" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D139" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>KdD11Mw1</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C140" t="n">
+        <v>4</v>
+      </c>
+      <c r="D140" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>MqxqEaN6</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C141" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>CW9g3r9l</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C142" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D142" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>pzHxyrtm</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>8</v>
+      </c>
+      <c r="C143" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>dCPKovw8</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>11</v>
+      </c>
+      <c r="C144" t="n">
+        <v>6</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>vXAKoaf5</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>3</v>
+      </c>
+      <c r="C145" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D145" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>YV3TqwPH</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>23</v>
+      </c>
+      <c r="C146" t="n">
+        <v>11</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>l0ueP5rR</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C147" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>t2AoZLAa</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>23</v>
+      </c>
+      <c r="C148" t="n">
+        <v>11</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>jFMCm08e</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C149" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>tvOIPExA</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C150" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>KSwfVwAO</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>19</v>
+      </c>
+      <c r="C151" t="n">
+        <v>10</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>6q2yrHgU</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C152" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D152" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>AiJ3kset</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>12</v>
+      </c>
+      <c r="C153" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D153" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>hzyf0b9b</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C154" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>CpiTEcOi</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C155" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D155" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>8CpxDyg4</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>41</v>
+      </c>
+      <c r="C156" t="n">
+        <v>19</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>bF2q76Mr</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>21</v>
+      </c>
+      <c r="C157" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>vyk5gjdE</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>15</v>
+      </c>
+      <c r="C158" t="n">
+        <v>7</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>tbKZHNz1</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C159" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D159" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>MZjh9ghT</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>15</v>
+      </c>
+      <c r="C160" t="n">
+        <v>7</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>f1nnRRDE</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>5</v>
+      </c>
+      <c r="C161" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>8QPARz8c</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>17</v>
+      </c>
+      <c r="C162" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>0K2qBFNG</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C163" t="n">
+        <v>5</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>Kj4sifWp</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>34</v>
+      </c>
+      <c r="C164" t="n">
+        <v>12</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>lONsG15D</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>19</v>
+      </c>
+      <c r="C165" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>pWQQJq6l</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C166" t="n">
+        <v>5</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>hIsO3XFj</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="C167" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>EF8gXauC</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>6</v>
+      </c>
+      <c r="C168" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>fcxqFy2l</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C169" t="n">
+        <v>4</v>
+      </c>
+      <c r="D169" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>06NAdG8N</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>41.00</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>1.04</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D173"/>
+  <dimension ref="A1:D185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3139,20 +3139,14 @@
           <t>pAXo2Kvn</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
+      <c r="B170" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="C170" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1.53</v>
       </c>
     </row>
     <row r="171">
@@ -3161,20 +3155,14 @@
           <t>06NAdG8N</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>9.50</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
+      <c r="B171" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C171" t="n">
+        <v>6</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1.27</v>
       </c>
     </row>
     <row r="172">
@@ -3183,20 +3171,14 @@
           <t>Sff03OL7</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
+      <c r="B172" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C172" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1.91</v>
       </c>
     </row>
     <row r="173">
@@ -3205,19 +3187,277 @@
           <t>EkP2bxvB</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>41.00</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>1.04</t>
+      <c r="B173" t="n">
+        <v>41</v>
+      </c>
+      <c r="C173" t="n">
+        <v>15</v>
+      </c>
+      <c r="D173" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>SxFxJ44k</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>YZZcMwBs</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>GbeXvnR8</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>O48oHrZ1</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>2FREIeA6</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>dfO6OQtS</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>zuzbQnCF</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>S2GROGyP</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>IReyqKMt</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>lGJRqVt2</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>800QQx7C</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>zm2ISbx0</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>4.50</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D185"/>
+  <dimension ref="A1:D191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3203,20 +3203,14 @@
           <t>SxFxJ44k</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B174" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C174" t="n">
+        <v>4</v>
+      </c>
+      <c r="D174" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="175">
@@ -3225,20 +3219,14 @@
           <t>YZZcMwBs</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B175" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C175" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D175" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="176">
@@ -3247,20 +3235,14 @@
           <t>GbeXvnR8</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
+      <c r="B176" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C176" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1.91</v>
       </c>
     </row>
     <row r="177">
@@ -3269,20 +3251,14 @@
           <t>O48oHrZ1</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B177" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C177" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D177" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="178">
@@ -3291,20 +3267,14 @@
           <t>2FREIeA6</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
+      <c r="B178" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C178" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D178" t="n">
+        <v>3.75</v>
       </c>
     </row>
     <row r="179">
@@ -3313,20 +3283,14 @@
           <t>dfO6OQtS</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
+      <c r="B179" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C179" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D179" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="180">
@@ -3335,20 +3299,14 @@
           <t>zuzbQnCF</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
+      <c r="B180" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C180" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D180" t="n">
+        <v>1.62</v>
       </c>
     </row>
     <row r="181">
@@ -3357,20 +3315,14 @@
           <t>S2GROGyP</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="B181" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C181" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D181" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="182">
@@ -3379,20 +3331,14 @@
           <t>IReyqKMt</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B182" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C182" t="n">
+        <v>4</v>
+      </c>
+      <c r="D182" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="183">
@@ -3401,20 +3347,14 @@
           <t>lGJRqVt2</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B183" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C183" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D183" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="184">
@@ -3423,20 +3363,14 @@
           <t>800QQx7C</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="B184" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C184" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D184" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="185">
@@ -3445,19 +3379,145 @@
           <t>zm2ISbx0</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>4.50</t>
+      <c r="B185" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C185" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D185" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>AuVMGZvJ</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>t0w6KHuf</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>vL89UK7m</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>vsppsbig</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>n7mhuxM5</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>8xIwzspQ</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>6.25</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D191"/>
+  <dimension ref="A1:D196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3395,20 +3395,14 @@
           <t>AuVMGZvJ</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
+      <c r="B186" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C186" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D186" t="n">
+        <v>3.75</v>
       </c>
     </row>
     <row r="187">
@@ -3417,20 +3411,14 @@
           <t>t0w6KHuf</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
+      <c r="B187" t="n">
+        <v>6</v>
+      </c>
+      <c r="C187" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D187" t="n">
+        <v>1.45</v>
       </c>
     </row>
     <row r="188">
@@ -3439,20 +3427,14 @@
           <t>vL89UK7m</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B188" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C188" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D188" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="189">
@@ -3461,20 +3443,14 @@
           <t>vsppsbig</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
+      <c r="B189" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C189" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D189" t="n">
+        <v>2.88</v>
       </c>
     </row>
     <row r="190">
@@ -3483,20 +3459,14 @@
           <t>n7mhuxM5</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="B190" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C190" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D190" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="191">
@@ -3505,19 +3475,123 @@
           <t>8xIwzspQ</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>6.25</t>
+      <c r="B191" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C191" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D191" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>djSMofvg</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>SGe0wGjI</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>vs08wy8F</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>6u6i5pie</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>29.00</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>W67CmLPh</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>1.22</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D196"/>
+  <dimension ref="A1:D206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3491,20 +3491,14 @@
           <t>djSMofvg</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B192" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C192" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D192" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="193">
@@ -3513,20 +3507,14 @@
           <t>SGe0wGjI</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B193" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C193" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D193" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="194">
@@ -3535,20 +3523,14 @@
           <t>vs08wy8F</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
+      <c r="B194" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C194" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D194" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="195">
@@ -3557,20 +3539,14 @@
           <t>6u6i5pie</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>29.00</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
+      <c r="B195" t="n">
+        <v>29</v>
+      </c>
+      <c r="C195" t="n">
+        <v>13</v>
+      </c>
+      <c r="D195" t="n">
+        <v>1.06</v>
       </c>
     </row>
     <row r="196">
@@ -3579,19 +3555,233 @@
           <t>W67CmLPh</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>1.22</t>
+      <c r="B196" t="n">
+        <v>9</v>
+      </c>
+      <c r="C196" t="n">
+        <v>7</v>
+      </c>
+      <c r="D196" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>U3QUqY85</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>AgAeVYgC</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>QVJwrCwI</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>jLJDHgod</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>A33XyOWA</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>0Ug8yfLU</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>fgQ4JFGq</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2.80</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D206"/>
+  <dimension ref="A1:D211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3571,20 +3571,14 @@
           <t>AVR8vwXP</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B197" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C197" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D197" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="198">
@@ -3593,20 +3587,14 @@
           <t>U3QUqY85</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="B198" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C198" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D198" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="199">
@@ -3615,20 +3603,14 @@
           <t>AgAeVYgC</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B199" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C199" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D199" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="200">
@@ -3637,20 +3619,14 @@
           <t>QVJwrCwI</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="B200" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C200" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D200" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="201">
@@ -3659,20 +3635,14 @@
           <t>61DvZGfm</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B201" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C201" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D201" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="202">
@@ -3681,20 +3651,14 @@
           <t>0OYDmG9t</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
+      <c r="B202" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C202" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1.91</v>
       </c>
     </row>
     <row r="203">
@@ -3703,20 +3667,14 @@
           <t>jLJDHgod</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B203" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C203" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D203" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -3725,20 +3683,14 @@
           <t>A33XyOWA</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="B204" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C204" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D204" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="205">
@@ -3747,20 +3699,14 @@
           <t>0Ug8yfLU</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="B205" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C205" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D205" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="206">
@@ -3769,19 +3715,123 @@
           <t>fgQ4JFGq</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
+      <c r="B206" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C206" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D206" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>2T6mXfPa</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>W8b4TCOO</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>rF6aucw3</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>tOBGu6Xo</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>llFOwp2b</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
         <is>
           <t>3.30</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>2.80</t>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2.05</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D223"/>
+  <dimension ref="A1:D229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3811,20 +3811,14 @@
           <t>x4pn9lxH</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
+      <c r="B212" t="n">
+        <v>11</v>
+      </c>
+      <c r="C212" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D212" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="213">
@@ -3833,20 +3827,14 @@
           <t>UwsvBA74</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B213" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C213" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D213" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="214">
@@ -3855,20 +3843,14 @@
           <t>vZqDdBhB</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
+      <c r="B214" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C214" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D214" t="n">
+        <v>5.75</v>
       </c>
     </row>
     <row r="215">
@@ -3877,20 +3859,14 @@
           <t>r7j4bXNb</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
+      <c r="B215" t="n">
+        <v>7</v>
+      </c>
+      <c r="C215" t="n">
+        <v>5</v>
+      </c>
+      <c r="D215" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="216">
@@ -3899,20 +3875,14 @@
           <t>WSMotj8U</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
+      <c r="B216" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C216" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D216" t="n">
+        <v>6.25</v>
       </c>
     </row>
     <row r="217">
@@ -3921,20 +3891,14 @@
           <t>tI0qkTpo</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B217" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C217" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D217" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="218">
@@ -3943,20 +3907,14 @@
           <t>zsmd0ggn</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
+      <c r="B218" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C218" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D218" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="219">
@@ -3965,20 +3923,14 @@
           <t>UBvmWh0k</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B219" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C219" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D219" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="220">
@@ -3987,20 +3939,14 @@
           <t>QcOkjEiL</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B220" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C220" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D220" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="221">
@@ -4009,20 +3955,14 @@
           <t>O8YUtAE7</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B221" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C221" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D221" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="222">
@@ -4031,20 +3971,14 @@
           <t>hpQshzN8</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B222" t="n">
+        <v>2</v>
+      </c>
+      <c r="C222" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D222" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="223">
@@ -4053,19 +3987,145 @@
           <t>jFQG4D6E</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
+      <c r="B223" t="n">
+        <v>3</v>
+      </c>
+      <c r="C223" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D223" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>8OhVCWxh</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>CnrLfkNN</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
         <is>
           <t>3.90</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>2.10</t>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>fTtEphFr</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>xxreUWU1</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>2gpMrWqe</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>pv3GyFxS</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>5.75</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D223"/>
+  <dimension ref="A1:D247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3811,20 +3811,14 @@
           <t>x4pn9lxH</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
+      <c r="B212" t="n">
+        <v>11</v>
+      </c>
+      <c r="C212" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D212" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="213">
@@ -3833,20 +3827,14 @@
           <t>UwsvBA74</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B213" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C213" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D213" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="214">
@@ -3855,20 +3843,14 @@
           <t>vZqDdBhB</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
+      <c r="B214" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C214" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D214" t="n">
+        <v>5.75</v>
       </c>
     </row>
     <row r="215">
@@ -3877,20 +3859,14 @@
           <t>r7j4bXNb</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
+      <c r="B215" t="n">
+        <v>7</v>
+      </c>
+      <c r="C215" t="n">
+        <v>5</v>
+      </c>
+      <c r="D215" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="216">
@@ -3899,20 +3875,14 @@
           <t>WSMotj8U</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
+      <c r="B216" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C216" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D216" t="n">
+        <v>6.25</v>
       </c>
     </row>
     <row r="217">
@@ -3921,20 +3891,14 @@
           <t>tI0qkTpo</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B217" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C217" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D217" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="218">
@@ -3943,20 +3907,14 @@
           <t>zsmd0ggn</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
+      <c r="B218" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C218" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D218" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="219">
@@ -3965,20 +3923,14 @@
           <t>UBvmWh0k</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B219" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C219" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D219" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="220">
@@ -3987,20 +3939,14 @@
           <t>QcOkjEiL</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B220" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C220" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D220" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="221">
@@ -4009,20 +3955,14 @@
           <t>O8YUtAE7</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B221" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C221" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D221" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="222">
@@ -4031,20 +3971,14 @@
           <t>hpQshzN8</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="B222" t="n">
+        <v>2</v>
+      </c>
+      <c r="C222" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D222" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="223">
@@ -4053,19 +3987,541 @@
           <t>jFQG4D6E</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B223" t="n">
+        <v>3</v>
+      </c>
+      <c r="C223" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D223" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
         <is>
           <t>3.00</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>pY1dP0SE</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
         <is>
           <t>3.90</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>dCL13J5e</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>8OhVCWxh</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>CnrLfkNN</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>px2CgmbD</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>WYJwA8rf</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>0EBf6QsJ</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>z7QUBUDs</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>4nIo8nD6</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
         <is>
           <t>2.10</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>pEJP2iyR</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>QXvaHjjK</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>tp5ecVbl</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>xCb4e9T0</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>fTtEphFr</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>xxreUWU1</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>2gpMrWqe</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>pv3GyFxS</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>5.75</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D247"/>
+  <dimension ref="A1:D260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4003,20 +4003,14 @@
           <t>dQ0zIIKl</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
+      <c r="B224" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C224" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D224" t="n">
+        <v>1.62</v>
       </c>
     </row>
     <row r="225">
@@ -4025,20 +4019,14 @@
           <t>2k0SlKj2</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B225" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C225" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D225" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="226">
@@ -4047,20 +4035,14 @@
           <t>Uy2KjtMk</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>8.50</t>
-        </is>
+      <c r="B226" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="C226" t="n">
+        <v>6</v>
+      </c>
+      <c r="D226" t="n">
+        <v>8.5</v>
       </c>
     </row>
     <row r="227">
@@ -4069,20 +4051,14 @@
           <t>IcrFCNr9</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B227" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C227" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D227" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="228">
@@ -4091,20 +4067,14 @@
           <t>pY1dP0SE</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B228" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C228" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D228" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="229">
@@ -4113,20 +4083,14 @@
           <t>QNoNA1DL</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="B229" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C229" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D229" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="230">
@@ -4135,20 +4099,14 @@
           <t>hvFA1cz8</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B230" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C230" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D230" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="231">
@@ -4157,20 +4115,14 @@
           <t>AeNg5uyq</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>8.50</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
+      <c r="B231" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C231" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D231" t="n">
+        <v>1.33</v>
       </c>
     </row>
     <row r="232">
@@ -4179,20 +4131,14 @@
           <t>dCL13J5e</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B232" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C232" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D232" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="233">
@@ -4201,20 +4147,14 @@
           <t>8OhVCWxh</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B233" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C233" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D233" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="234">
@@ -4223,20 +4163,14 @@
           <t>CnrLfkNN</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="B234" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C234" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D234" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="235">
@@ -4245,20 +4179,14 @@
           <t>px2CgmbD</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
+      <c r="B235" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C235" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D235" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="236">
@@ -4267,20 +4195,14 @@
           <t>WYJwA8rf</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="B236" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C236" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D236" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="237">
@@ -4289,20 +4211,14 @@
           <t>0EBf6QsJ</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B237" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C237" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D237" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="238">
@@ -4311,20 +4227,14 @@
           <t>z7QUBUDs</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B238" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C238" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D238" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="239">
@@ -4333,20 +4243,14 @@
           <t>4nIo8nD6</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B239" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C239" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D239" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="240">
@@ -4355,20 +4259,14 @@
           <t>pEJP2iyR</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B240" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C240" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D240" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="241">
@@ -4377,20 +4275,14 @@
           <t>QXvaHjjK</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B241" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C241" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D241" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="242">
@@ -4399,20 +4291,14 @@
           <t>tp5ecVbl</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B242" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C242" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D242" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="243">
@@ -4421,20 +4307,14 @@
           <t>xCb4e9T0</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="B243" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C243" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D243" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="244">
@@ -4443,20 +4323,14 @@
           <t>fTtEphFr</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B244" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C244" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D244" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="245">
@@ -4465,20 +4339,14 @@
           <t>xxreUWU1</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
+      <c r="B245" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C245" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D245" t="n">
+        <v>6.25</v>
       </c>
     </row>
     <row r="246">
@@ -4487,20 +4355,14 @@
           <t>2gpMrWqe</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B246" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C246" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D246" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="247">
@@ -4509,19 +4371,299 @@
           <t>pv3GyFxS</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>5.75</t>
+      <c r="B247" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C247" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D247" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>rsNyMnwK</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>vwAdMxYG</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>WjVDBLJb</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>vHYL9alB</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>n3D4KG2T</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>WED02Hto</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>INLmOb34</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2.63</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D260"/>
+  <dimension ref="A1:D265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4387,20 +4387,14 @@
           <t>IukqGdk1</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B248" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C248" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D248" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="249">
@@ -4409,20 +4403,14 @@
           <t>CIlrT3pm</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="B249" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C249" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D249" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="250">
@@ -4431,20 +4419,14 @@
           <t>6uSGCr06</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="B250" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C250" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D250" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="251">
@@ -4453,20 +4435,14 @@
           <t>f18BYPMP</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B251" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C251" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D251" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="252">
@@ -4475,20 +4451,14 @@
           <t>Q5hiEzKD</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="B252" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C252" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D252" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="253">
@@ -4497,20 +4467,14 @@
           <t>SfGPAMUI</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="B253" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C253" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D253" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -4519,20 +4483,14 @@
           <t>rsNyMnwK</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
+      <c r="B254" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C254" t="n">
+        <v>7</v>
+      </c>
+      <c r="D254" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="255">
@@ -4541,20 +4499,14 @@
           <t>vwAdMxYG</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="B255" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C255" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D255" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="256">
@@ -4563,20 +4515,14 @@
           <t>WjVDBLJb</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="B256" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C256" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D256" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="257">
@@ -4585,20 +4531,14 @@
           <t>vHYL9alB</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="B257" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C257" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D257" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="258">
@@ -4607,20 +4547,14 @@
           <t>n3D4KG2T</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="B258" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C258" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D258" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="259">
@@ -4629,20 +4563,14 @@
           <t>WED02Hto</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="B259" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C259" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D259" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="260">
@@ -4651,19 +4579,123 @@
           <t>INLmOb34</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>2.63</t>
+      <c r="B260" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C260" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D260" t="n">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>Ays5Dskn</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>zqSU7wJN</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>AcIuQKYi</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>3.90</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D276"/>
+  <dimension ref="A1:D283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4675,20 +4675,14 @@
           <t>zwD8uYZ9</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B266" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C266" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D266" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="267">
@@ -4697,20 +4691,14 @@
           <t>tbtaPLqC</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
+      <c r="B267" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="C267" t="n">
+        <v>12</v>
+      </c>
+      <c r="D267" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="268">
@@ -4719,20 +4707,14 @@
           <t>ENOasf5c</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="B268" t="n">
+        <v>3</v>
+      </c>
+      <c r="C268" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D268" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="269">
@@ -4741,20 +4723,14 @@
           <t>lpXDJjDj</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="B269" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C269" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D269" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -4763,20 +4739,14 @@
           <t>dnhZQYKG</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="B270" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C270" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D270" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="271">
@@ -4785,20 +4755,14 @@
           <t>UajsPCkT</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="B271" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C271" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D271" t="n">
+        <v>2.75</v>
       </c>
     </row>
     <row r="272">
@@ -4807,20 +4771,14 @@
           <t>I5SHRX9d</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="B272" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C272" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D272" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="273">
@@ -4829,20 +4787,14 @@
           <t>4KgyFfQj</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
+      <c r="B273" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="C273" t="n">
+        <v>6</v>
+      </c>
+      <c r="D273" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="274">
@@ -4851,20 +4803,14 @@
           <t>YDA4ky23</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B274" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C274" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D274" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="275">
@@ -4873,20 +4819,14 @@
           <t>htzWzxmA</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="B275" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C275" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D275" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="276">
@@ -4895,19 +4835,167 @@
           <t>06wvZFHM</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>7.00</t>
+      <c r="B276" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="C276" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D276" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>2g2Log1S</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>dEtNxbIc</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>6R8CmFWF</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>pvFATgup</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>2.80</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D283"/>
+  <dimension ref="A1:D295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4851,20 +4851,14 @@
           <t>nc8W6DTp</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="B277" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C277" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D277" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="278">
@@ -4873,20 +4867,14 @@
           <t>ShoJUGLi</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
+      <c r="B278" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="C278" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D278" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="279">
@@ -4895,20 +4883,14 @@
           <t>0KbQSfj4</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
+      <c r="B279" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C279" t="n">
+        <v>4</v>
+      </c>
+      <c r="D279" t="n">
+        <v>1.67</v>
       </c>
     </row>
     <row r="280">
@@ -4917,20 +4899,14 @@
           <t>2g2Log1S</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
+      <c r="B280" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C280" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D280" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="281">
@@ -4939,20 +4915,14 @@
           <t>dEtNxbIc</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="B281" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C281" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D281" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="282">
@@ -4961,20 +4931,14 @@
           <t>6R8CmFWF</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="B282" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C282" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D282" t="n">
+        <v>3.5</v>
       </c>
     </row>
     <row r="283">
@@ -4983,19 +4947,277 @@
           <t>pvFATgup</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
+      <c r="B283" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C283" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D283" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>2mcmYkSq</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>fHjVr7t2</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
         <is>
           <t>3.70</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>2.80</t>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>r3GGwC4M</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>M93rhBJF</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>Eq0zfXl3</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>E7rNpTBk</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>z1eeWTdd</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>KUYo2Eo9</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>r9D87Uvn</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>l6GG589b</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>W8hitXOk</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>nqkSsp0f</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>3.70</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D295"/>
+  <dimension ref="A1:D301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4963,20 +4963,14 @@
           <t>2mcmYkSq</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
+      <c r="B284" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C284" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D284" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="285">
@@ -4985,20 +4979,14 @@
           <t>fHjVr7t2</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="B285" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C285" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D285" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="286">
@@ -5007,20 +4995,14 @@
           <t>r3GGwC4M</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="B286" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C286" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D286" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="287">
@@ -5029,20 +5011,14 @@
           <t>M93rhBJF</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B287" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C287" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D287" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="288">
@@ -5051,20 +5027,14 @@
           <t>Eq0zfXl3</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B288" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C288" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D288" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="289">
@@ -5073,20 +5043,14 @@
           <t>E7rNpTBk</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
+      <c r="B289" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C289" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D289" t="n">
+        <v>1.83</v>
       </c>
     </row>
     <row r="290">
@@ -5095,20 +5059,14 @@
           <t>z1eeWTdd</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
+      <c r="B290" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="C290" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D290" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="291">
@@ -5117,20 +5075,14 @@
           <t>KUYo2Eo9</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B291" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C291" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D291" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="292">
@@ -5139,20 +5091,14 @@
           <t>r9D87Uvn</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="B292" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C292" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D292" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="293">
@@ -5161,20 +5107,14 @@
           <t>l6GG589b</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
+      <c r="B293" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C293" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D293" t="n">
+        <v>1.75</v>
       </c>
     </row>
     <row r="294">
@@ -5183,20 +5123,14 @@
           <t>W8hitXOk</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
+      <c r="B294" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C294" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D294" t="n">
+        <v>1.9</v>
       </c>
     </row>
     <row r="295">
@@ -5205,19 +5139,145 @@
           <t>nqkSsp0f</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>3.70</t>
+      <c r="B295" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C295" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D295" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>rPiijklS</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>nBwH6AY8</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>EVjKq6Vs</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>hOt0vBg2</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>4rrbmRgU</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>6o5TuOU6</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>2.20</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D301"/>
+  <dimension ref="A1:D319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5155,20 +5155,14 @@
           <t>rPiijklS</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B296" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="C296" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D296" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="297">
@@ -5177,20 +5171,14 @@
           <t>nBwH6AY8</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="B297" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C297" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D297" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="298">
@@ -5199,20 +5187,14 @@
           <t>EVjKq6Vs</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B298" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C298" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D298" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="299">
@@ -5221,20 +5203,14 @@
           <t>hOt0vBg2</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B299" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C299" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D299" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="300">
@@ -5243,20 +5219,14 @@
           <t>4rrbmRgU</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
+      <c r="B300" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C300" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D300" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="301">
@@ -5265,19 +5235,337 @@
           <t>6o5TuOU6</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>2.20</t>
+      <c r="B301" t="n">
+        <v>3</v>
+      </c>
+      <c r="C301" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D301" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>MiACepQ7</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="C302" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D302" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>x0haJmIE</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>4</v>
+      </c>
+      <c r="C303" t="n">
+        <v>4</v>
+      </c>
+      <c r="D303" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>ELNeaSQr</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C304" t="n">
+        <v>4</v>
+      </c>
+      <c r="D304" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>Mku6FvHt</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C305" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D305" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>rwXP4l3L</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C306" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D306" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>4E8uaJWa</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C307" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D307" t="n">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>xWl4d4Wp</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C308" t="n">
+        <v>4</v>
+      </c>
+      <c r="D308" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>r3AbGPNG</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C309" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D309" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>UPyjK7Oi</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C310" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D310" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>zw7jIog4</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C311" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D311" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>AL4P3nvB</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C312" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D312" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2iNWcH7k</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C313" t="n">
+        <v>4</v>
+      </c>
+      <c r="D313" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>zyC4c6ee</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>ABBmcc1C</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>WQadeyWO</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>Od8RJbU8</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>Io8X1Q8N</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>AHQvdex2</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>2.70</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D319"/>
+  <dimension ref="A1:D335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5443,20 +5443,14 @@
           <t>zyC4c6ee</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="B314" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C314" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D314" t="n">
+        <v>2.55</v>
       </c>
     </row>
     <row r="315">
@@ -5465,20 +5459,14 @@
           <t>ABBmcc1C</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>2.87</t>
-        </is>
+      <c r="B315" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C315" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D315" t="n">
+        <v>2.87</v>
       </c>
     </row>
     <row r="316">
@@ -5487,20 +5475,14 @@
           <t>WQadeyWO</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>9.50</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
+      <c r="B316" t="n">
+        <v>11</v>
+      </c>
+      <c r="C316" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D316" t="n">
+        <v>1.17</v>
       </c>
     </row>
     <row r="317">
@@ -5509,20 +5491,14 @@
           <t>Od8RJbU8</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="B317" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C317" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D317" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="318">
@@ -5531,20 +5507,14 @@
           <t>Io8X1Q8N</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B318" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C318" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D318" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="319">
@@ -5553,19 +5523,365 @@
           <t>AHQvdex2</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
+      <c r="B319" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C319" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D319" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>84x8UQRb</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>6yf7a6SO</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>UyxiUHXF</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>YNea1ScC</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>dQ8kCqCU</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>0bFtE5sI</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>YkhlAdtp</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>tGed8zBd</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
         <is>
           <t>2.45</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>2.70</t>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>EsHYFRC5</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>CxqaWncn</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>hSSPHmrg</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>E1uGS4dB</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>6XcNMZPk</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>zk7iSe2S</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>dOwqWw33</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>p2PHJ9Dt</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>5.25</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D335"/>
+  <dimension ref="A1:D353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5539,20 +5539,14 @@
           <t>84x8UQRb</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
+      <c r="B320" t="n">
+        <v>5</v>
+      </c>
+      <c r="C320" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D320" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="321">
@@ -5561,20 +5555,14 @@
           <t>6yf7a6SO</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
+      <c r="B321" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C321" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D321" t="n">
+        <v>6.25</v>
       </c>
     </row>
     <row r="322">
@@ -5583,20 +5571,14 @@
           <t>UyxiUHXF</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
+      <c r="B322" t="n">
+        <v>11</v>
+      </c>
+      <c r="C322" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D322" t="n">
+        <v>1.22</v>
       </c>
     </row>
     <row r="323">
@@ -5605,20 +5587,14 @@
           <t>YNea1ScC</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="B323" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C323" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D323" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="324">
@@ -5627,20 +5603,14 @@
           <t>dQ8kCqCU</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="B324" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C324" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D324" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="325">
@@ -5649,20 +5619,14 @@
           <t>0bFtE5sI</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B325" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C325" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D325" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="326">
@@ -5671,20 +5635,14 @@
           <t>YkhlAdtp</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+      <c r="B326" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C326" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D326" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="327">
@@ -5693,20 +5651,14 @@
           <t>tGed8zBd</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+      <c r="B327" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C327" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D327" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="328">
@@ -5715,20 +5667,14 @@
           <t>EsHYFRC5</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B328" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C328" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D328" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="329">
@@ -5737,20 +5683,14 @@
           <t>CxqaWncn</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="B329" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C329" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D329" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="330">
@@ -5759,20 +5699,14 @@
           <t>hSSPHmrg</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="B330" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C330" t="n">
+        <v>5</v>
+      </c>
+      <c r="D330" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="331">
@@ -5781,20 +5715,14 @@
           <t>E1uGS4dB</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="B331" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C331" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D331" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="332">
@@ -5803,20 +5731,14 @@
           <t>6XcNMZPk</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>8.50</t>
-        </is>
+      <c r="B332" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C332" t="n">
+        <v>5</v>
+      </c>
+      <c r="D332" t="n">
+        <v>8.5</v>
       </c>
     </row>
     <row r="333">
@@ -5825,20 +5747,14 @@
           <t>zk7iSe2S</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
+      <c r="B333" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="C333" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D333" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="334">
@@ -5847,20 +5763,14 @@
           <t>dOwqWw33</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
+      <c r="B334" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C334" t="n">
+        <v>4</v>
+      </c>
+      <c r="D334" t="n">
+        <v>1.83</v>
       </c>
     </row>
     <row r="335">
@@ -5869,19 +5779,409 @@
           <t>p2PHJ9Dt</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
+      <c r="B335" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C335" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D335" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>raQ4MDUN</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>GnZmQeVb</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>dr2N9zoI</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>jVWMBdG5</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>485V7EFU</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>8MVuSH0n</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2q7yHiho</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>AoSdOZaB</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>IHYEDIog</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>dA6ZHxaL</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
         <is>
           <t>1.67</t>
         </is>
       </c>
-      <c r="C335" t="inlineStr">
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>naLHUFrR</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>OKjEAfie</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>jXR8WyEE</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
         <is>
           <t>3.60</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>5.25</t>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>pzuN8YL7</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>Gfm6CGMr</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>W4I3LB5D</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>vc0dNXz1</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>rV6mPg6l</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>2.70</t>
         </is>
       </c>
     </row>
